--- a/docs/IDEA_TRACKER.xlsx
+++ b/docs/IDEA_TRACKER.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1528,6 +1528,396 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:08</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>All important Indian languages</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Telugu, Tamil, Kannada, Malayalam, Marathi, Bengali, Gujarati, Punjabi, Odia, Assamese + Hindi via Meta MMS-TTS.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11 Indian languages live, 18 total. Verified Telugu/Tamil/Hindi generate real audio at 16kHz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:08</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Volume control</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Slider in the sidebar.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0-3x, clipped to avoid waveform wrap/crackle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:08</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Replace push-to-talk with hands-free</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>User disliked clicking a button each turn.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Hands-free toggle: auto-listens after each reply. Off by default and stops the moment it is switched off, given the earlier mic-privacy concern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:08</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Multiple Telugu voices/accents (IndicF5)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MMS gives ONE voice per language. AI4Bharat IndicF5 does voice cloning from reference audio -&gt; multiple accents.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>waiting_on_user</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>IndicF5 is a GATED HF model -- needs you to request access on your Hugging Face account, then an HF token.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:08</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Photorealistic face for LIVE speaking</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3D avatars look like game characters; that is the ceiling of real-time WebGL rendering.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>waiting_on_user</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Best available improvement: generate an avatar from YOUR photo at avaturn.me and send the .glb. True photorealism needs SadTalker video (~5 min/reply, not live).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Latency: tool pre-pass gated</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Tool-detection pass cost ~18s of every ~20s reply, even for "say hi".</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Keyword gate. Ordinary chat 20s -&gt; 3.4s measured. Commit 3759b17.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fix model deflecting real tool data</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Tools fetched correct values, model still said "I do not have real-time access".</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tool result now named + restated plainly. Verified: stock/weather/sports all answer with real figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Switch webrtcvad -&gt; Silero VAD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Research (RealtimeSTT, open-gpt-live, 2026 consensus stack): Silero VAD v5 is markedly better at end-of-speech detection than WebRTC VAD.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Would reduce mid-sentence cut-offs. RealtimeSTT wraps both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Overlap transcription with recording</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Currently sequential: record fully, then transcribe. Best practice is rolling chunks so transcription finishes the instant you stop talking.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>RealtimeSTT does this out of the box.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:40</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>FastAPI + WebSocket live server (true barge-in)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Streamlit cannot interrupt server-side sounddevice playback; needed a bidirectional transport.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>server.py + static/live/index.html + Krishna Live.bat. Imports krishna.py unchanged. Verified over a real WS: full loop then stop(reason=barge-in). Port 8611.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:40</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Silero VAD replaces webrtcvad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Better end-of-speech detection.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>speech 0.744 vs noise 0.007 mean probability; auto-fallback to webrtcvad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:40</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Fix MMS crash on wrong-script text</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>prepare_voice warmed up with "ok"; Indian tokenizers have no Latin chars -&gt; 0 tokens -&gt; crash.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Load split from inference; wrong-script text now skipped gracefully. Also covers LLM replying in English while Telugu selected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-13 23:40</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Rolling transcription</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Overlap transcription with recording.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>dropped</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Measured transcribe() at 0.75s for 4.7s audio (6x realtime) -- would save &lt;1s. Not worth the rewrite risk.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
